--- a/material/Week5-Tradeoffs/Week5-Skillcheck.xlsx
+++ b/material/Week5-Tradeoffs/Week5-Skillcheck.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mailmissouri-my.sharepoint.com/personal/btdhd_umsystem_edu/Documents/Desktop/NATR_8001_DecisionAnalysis_Fall25_Mizzou/material/Week5-Tradeoffs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{E84E3B57-7A07-4D7D-A693-35ADA1845EE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{72BB7984-2642-427A-B283-10C447874C5F}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="8_{E84E3B57-7A07-4D7D-A693-35ADA1845EE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{288547FB-48F0-4BCD-BD23-7B316A3C41C0}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8E6094A0-F1BF-4785-B38D-3B1B58DBD82F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{8E6094A0-F1BF-4785-B38D-3B1B58DBD82F}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -965,6 +965,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1285,10 +1289,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93F4B47D-A9BB-48AC-8480-CD7E4C5E1576}">
   <dimension ref="B1:N35"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="2" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B2" s="58" t="s">
         <v>42</v>
       </c>
@@ -1305,7 +1309,7 @@
       <c r="M2" s="59"/>
       <c r="N2" s="60"/>
     </row>
-    <row r="3" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B3" s="61"/>
       <c r="C3" s="62"/>
       <c r="D3" s="62"/>
@@ -1320,7 +1324,7 @@
       <c r="M3" s="62"/>
       <c r="N3" s="63"/>
     </row>
-    <row r="4" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B4" s="61"/>
       <c r="C4" s="62"/>
       <c r="D4" s="62"/>
@@ -1335,7 +1339,7 @@
       <c r="M4" s="62"/>
       <c r="N4" s="63"/>
     </row>
-    <row r="5" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B5" s="61"/>
       <c r="C5" s="62"/>
       <c r="D5" s="62"/>
@@ -1350,7 +1354,7 @@
       <c r="M5" s="62"/>
       <c r="N5" s="63"/>
     </row>
-    <row r="6" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B6" s="61"/>
       <c r="C6" s="62"/>
       <c r="D6" s="62"/>
@@ -1365,7 +1369,7 @@
       <c r="M6" s="62"/>
       <c r="N6" s="63"/>
     </row>
-    <row r="7" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B7" s="61"/>
       <c r="C7" s="62"/>
       <c r="D7" s="62"/>
@@ -1380,7 +1384,7 @@
       <c r="M7" s="62"/>
       <c r="N7" s="63"/>
     </row>
-    <row r="8" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B8" s="61"/>
       <c r="C8" s="62"/>
       <c r="D8" s="62"/>
@@ -1395,7 +1399,7 @@
       <c r="M8" s="62"/>
       <c r="N8" s="63"/>
     </row>
-    <row r="9" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B9" s="61"/>
       <c r="C9" s="62"/>
       <c r="D9" s="62"/>
@@ -1410,7 +1414,7 @@
       <c r="M9" s="62"/>
       <c r="N9" s="63"/>
     </row>
-    <row r="10" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B10" s="61"/>
       <c r="C10" s="62"/>
       <c r="D10" s="62"/>
@@ -1425,7 +1429,7 @@
       <c r="M10" s="62"/>
       <c r="N10" s="63"/>
     </row>
-    <row r="11" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B11" s="61"/>
       <c r="C11" s="62"/>
       <c r="D11" s="62"/>
@@ -1440,7 +1444,7 @@
       <c r="M11" s="62"/>
       <c r="N11" s="63"/>
     </row>
-    <row r="12" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B12" s="61"/>
       <c r="C12" s="62"/>
       <c r="D12" s="62"/>
@@ -1455,7 +1459,7 @@
       <c r="M12" s="62"/>
       <c r="N12" s="63"/>
     </row>
-    <row r="13" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B13" s="61"/>
       <c r="C13" s="62"/>
       <c r="D13" s="62"/>
@@ -1470,7 +1474,7 @@
       <c r="M13" s="62"/>
       <c r="N13" s="63"/>
     </row>
-    <row r="14" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B14" s="61"/>
       <c r="C14" s="62"/>
       <c r="D14" s="62"/>
@@ -1485,7 +1489,7 @@
       <c r="M14" s="62"/>
       <c r="N14" s="63"/>
     </row>
-    <row r="15" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B15" s="61"/>
       <c r="C15" s="62"/>
       <c r="D15" s="62"/>
@@ -1500,7 +1504,7 @@
       <c r="M15" s="62"/>
       <c r="N15" s="63"/>
     </row>
-    <row r="16" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B16" s="61"/>
       <c r="C16" s="62"/>
       <c r="D16" s="62"/>
@@ -1515,7 +1519,7 @@
       <c r="M16" s="62"/>
       <c r="N16" s="63"/>
     </row>
-    <row r="17" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B17" s="61"/>
       <c r="C17" s="62"/>
       <c r="D17" s="62"/>
@@ -1530,7 +1534,7 @@
       <c r="M17" s="62"/>
       <c r="N17" s="63"/>
     </row>
-    <row r="18" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B18" s="61"/>
       <c r="C18" s="62"/>
       <c r="D18" s="62"/>
@@ -1545,7 +1549,7 @@
       <c r="M18" s="62"/>
       <c r="N18" s="63"/>
     </row>
-    <row r="19" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B19" s="61"/>
       <c r="C19" s="62"/>
       <c r="D19" s="62"/>
@@ -1560,7 +1564,7 @@
       <c r="M19" s="62"/>
       <c r="N19" s="63"/>
     </row>
-    <row r="20" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B20" s="61"/>
       <c r="C20" s="62"/>
       <c r="D20" s="62"/>
@@ -1575,7 +1579,7 @@
       <c r="M20" s="62"/>
       <c r="N20" s="63"/>
     </row>
-    <row r="21" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B21" s="61"/>
       <c r="C21" s="62"/>
       <c r="D21" s="62"/>
@@ -1590,7 +1594,7 @@
       <c r="M21" s="62"/>
       <c r="N21" s="63"/>
     </row>
-    <row r="22" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B22" s="61"/>
       <c r="C22" s="62"/>
       <c r="D22" s="62"/>
@@ -1605,7 +1609,7 @@
       <c r="M22" s="62"/>
       <c r="N22" s="63"/>
     </row>
-    <row r="23" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B23" s="61"/>
       <c r="C23" s="62"/>
       <c r="D23" s="62"/>
@@ -1620,7 +1624,7 @@
       <c r="M23" s="62"/>
       <c r="N23" s="63"/>
     </row>
-    <row r="24" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B24" s="61"/>
       <c r="C24" s="62"/>
       <c r="D24" s="62"/>
@@ -1635,7 +1639,7 @@
       <c r="M24" s="62"/>
       <c r="N24" s="63"/>
     </row>
-    <row r="25" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B25" s="61"/>
       <c r="C25" s="62"/>
       <c r="D25" s="62"/>
@@ -1650,7 +1654,7 @@
       <c r="M25" s="62"/>
       <c r="N25" s="63"/>
     </row>
-    <row r="26" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B26" s="61"/>
       <c r="C26" s="62"/>
       <c r="D26" s="62"/>
@@ -1665,7 +1669,7 @@
       <c r="M26" s="62"/>
       <c r="N26" s="63"/>
     </row>
-    <row r="27" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B27" s="61"/>
       <c r="C27" s="62"/>
       <c r="D27" s="62"/>
@@ -1680,7 +1684,7 @@
       <c r="M27" s="62"/>
       <c r="N27" s="63"/>
     </row>
-    <row r="28" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B28" s="61"/>
       <c r="C28" s="62"/>
       <c r="D28" s="62"/>
@@ -1695,7 +1699,7 @@
       <c r="M28" s="62"/>
       <c r="N28" s="63"/>
     </row>
-    <row r="29" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B29" s="61"/>
       <c r="C29" s="62"/>
       <c r="D29" s="62"/>
@@ -1710,7 +1714,7 @@
       <c r="M29" s="62"/>
       <c r="N29" s="63"/>
     </row>
-    <row r="30" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B30" s="61"/>
       <c r="C30" s="62"/>
       <c r="D30" s="62"/>
@@ -1725,7 +1729,7 @@
       <c r="M30" s="62"/>
       <c r="N30" s="63"/>
     </row>
-    <row r="31" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B31" s="61"/>
       <c r="C31" s="62"/>
       <c r="D31" s="62"/>
@@ -1740,7 +1744,7 @@
       <c r="M31" s="62"/>
       <c r="N31" s="63"/>
     </row>
-    <row r="32" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B32" s="64"/>
       <c r="C32" s="65"/>
       <c r="D32" s="65"/>
@@ -1755,7 +1759,7 @@
       <c r="M32" s="65"/>
       <c r="N32" s="66"/>
     </row>
-    <row r="35" spans="2:2" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="2:2" ht="24" x14ac:dyDescent="0.4">
       <c r="B35" s="31" t="s">
         <v>43</v>
       </c>
@@ -1771,22 +1775,22 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CEFBDD42-12EA-4BED-9E12-AAFD1F2477F3}">
   <dimension ref="B2:L26"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="22.81640625" customWidth="1"/>
-    <col min="4" max="4" width="12.08984375" customWidth="1"/>
-    <col min="5" max="7" width="12.08984375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="22.81640625" customWidth="1"/>
-    <col min="11" max="11" width="12.7265625" customWidth="1"/>
-    <col min="12" max="12" width="14.36328125" customWidth="1"/>
+    <col min="2" max="2" width="22.85546875" customWidth="1"/>
+    <col min="4" max="4" width="12.140625" customWidth="1"/>
+    <col min="5" max="7" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="22.85546875" customWidth="1"/>
+    <col min="11" max="11" width="12.7109375" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="2:12" ht="24" x14ac:dyDescent="0.4">
       <c r="B2" s="31" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="2:12" ht="19" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="3" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D3" s="67" t="s">
         <v>24</v>
       </c>
@@ -1794,7 +1798,7 @@
       <c r="F3" s="67"/>
       <c r="G3" s="67"/>
     </row>
-    <row r="4" spans="2:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="25" t="s">
         <v>3</v>
       </c>
@@ -1814,7 +1818,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="2:12" ht="32.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:12" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B5" s="27" t="s">
         <v>33</v>
       </c>
@@ -1840,7 +1844,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="6" spans="2:12" ht="35.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="2:12" ht="35.450000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B6" s="27" t="s">
         <v>10</v>
       </c>
@@ -1869,7 +1873,7 @@
         <v>0.1666</v>
       </c>
     </row>
-    <row r="7" spans="2:12" ht="32.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="2:12" ht="32.450000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B7" s="27" t="s">
         <v>12</v>
       </c>
@@ -1898,7 +1902,7 @@
         <v>0.1666</v>
       </c>
     </row>
-    <row r="8" spans="2:12" ht="40.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="2:12" ht="40.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B8" s="27" t="s">
         <v>13</v>
       </c>
@@ -1928,7 +1932,7 @@
         <v>0.1666</v>
       </c>
     </row>
-    <row r="9" spans="2:12" ht="32.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="2:12" ht="32.450000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B9" s="27" t="s">
         <v>14</v>
       </c>
@@ -1957,7 +1961,7 @@
         <v>0.1666</v>
       </c>
     </row>
-    <row r="10" spans="2:12" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="2:12" ht="32.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B10" s="29" t="s">
         <v>29</v>
       </c>
@@ -1986,7 +1990,7 @@
         <v>0.1666</v>
       </c>
     </row>
-    <row r="11" spans="2:12" ht="31" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="2:12" ht="32.25" thickBot="1" x14ac:dyDescent="0.4">
       <c r="J11" s="41" t="s">
         <v>29</v>
       </c>
@@ -1997,7 +2001,7 @@
         <v>0.1666</v>
       </c>
     </row>
-    <row r="12" spans="2:12" ht="76" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:12" ht="75.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="J12" s="50"/>
       <c r="K12" s="46" t="s">
         <v>31</v>
@@ -2006,12 +2010,12 @@
         <v>37</v>
       </c>
     </row>
-    <row r="13" spans="2:12" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="2:12" ht="24" x14ac:dyDescent="0.4">
       <c r="B13" s="31" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="2:12" ht="19" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="14" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D14" s="67" t="s">
         <v>24</v>
       </c>
@@ -2019,7 +2023,7 @@
       <c r="F14" s="67"/>
       <c r="G14" s="67"/>
     </row>
-    <row r="15" spans="2:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B15" s="25" t="s">
         <v>3</v>
       </c>
@@ -2039,7 +2043,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="16" spans="2:12" ht="29.5" x14ac:dyDescent="0.4">
+    <row r="16" spans="2:12" ht="30" x14ac:dyDescent="0.25">
       <c r="B16" s="27" t="s">
         <v>33</v>
       </c>
@@ -2066,7 +2070,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="17" spans="2:8" ht="29.5" x14ac:dyDescent="0.4">
+    <row r="17" spans="2:8" ht="30" x14ac:dyDescent="0.25">
       <c r="B17" s="27" t="s">
         <v>10</v>
       </c>
@@ -2093,7 +2097,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="18" spans="2:8" ht="29.5" x14ac:dyDescent="0.4">
+    <row r="18" spans="2:8" ht="45" x14ac:dyDescent="0.25">
       <c r="B18" s="27" t="s">
         <v>12</v>
       </c>
@@ -2117,7 +2121,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="19" spans="2:8" ht="29.5" x14ac:dyDescent="0.4">
+    <row r="19" spans="2:8" ht="30" x14ac:dyDescent="0.25">
       <c r="B19" s="27" t="s">
         <v>13</v>
       </c>
@@ -2141,7 +2145,7 @@
         <v>0.55555555555555558</v>
       </c>
     </row>
-    <row r="20" spans="2:8" ht="44" x14ac:dyDescent="0.4">
+    <row r="20" spans="2:8" ht="45" x14ac:dyDescent="0.25">
       <c r="B20" s="27" t="s">
         <v>14</v>
       </c>
@@ -2165,7 +2169,7 @@
         <v>0.46666666666666656</v>
       </c>
     </row>
-    <row r="21" spans="2:8" ht="30" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="21" spans="2:8" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B21" s="29" t="s">
         <v>30</v>
       </c>
@@ -2189,11 +2193,11 @@
         <v>0.45454545454545464</v>
       </c>
     </row>
-    <row r="22" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E22" s="24"/>
       <c r="F22" s="24"/>
     </row>
-    <row r="23" spans="2:8" ht="37.5" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="23" spans="2:8" ht="57" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B23" s="56" t="s">
         <v>34</v>
       </c>
@@ -2215,11 +2219,11 @@
         <v>0.53757949494949486</v>
       </c>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D24" s="32"/>
     </row>
-    <row r="25" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="26" spans="2:8" ht="37.5" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="25" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="26" spans="2:8" ht="38.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B26" s="57" t="s">
         <v>35</v>
       </c>
@@ -2272,18 +2276,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B530F8E-8ED6-4B10-8C37-128BAAAF4D41}">
   <dimension ref="B3:N14"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="23.81640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B3" s="22" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:14" x14ac:dyDescent="0.25">
       <c r="D4" s="68" t="s">
         <v>1</v>
       </c>
@@ -2297,7 +2301,7 @@
       <c r="J4" s="69"/>
       <c r="K4" s="69"/>
     </row>
-    <row r="5" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B5" s="2" t="s">
         <v>3</v>
       </c>
@@ -2332,7 +2336,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="2:14" ht="32.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:14" ht="32.450000000000003" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B6" s="2" t="s">
         <v>8</v>
       </c>
@@ -2355,7 +2359,7 @@
       <c r="K6" s="7"/>
       <c r="L6" s="7"/>
     </row>
-    <row r="7" spans="2:14" ht="32.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:14" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="2" t="s">
         <v>10</v>
       </c>
@@ -2378,7 +2382,7 @@
       <c r="K7" s="11"/>
       <c r="L7" s="11"/>
     </row>
-    <row r="8" spans="2:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="2" t="s">
         <v>12</v>
       </c>
@@ -2404,7 +2408,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="9" spans="2:14" ht="32.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:14" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="2" t="s">
         <v>13</v>
       </c>
@@ -2427,7 +2431,7 @@
       <c r="K9" s="11"/>
       <c r="L9" s="11"/>
     </row>
-    <row r="10" spans="2:14" ht="33.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:14" ht="33.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="2" t="s">
         <v>14</v>
       </c>
@@ -2450,7 +2454,7 @@
       <c r="K10" s="12"/>
       <c r="L10" s="11"/>
     </row>
-    <row r="11" spans="2:14" ht="32.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:14" ht="32.450000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B11" s="2" t="s">
         <v>15</v>
       </c>
@@ -2473,7 +2477,7 @@
       <c r="K11" s="14"/>
       <c r="L11" s="15"/>
     </row>
-    <row r="12" spans="2:14" ht="15" thickTop="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:14" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="D12" s="68" t="s">
         <v>16</v>
       </c>
@@ -2492,7 +2496,7 @@
       </c>
       <c r="N12" s="42"/>
     </row>
-    <row r="13" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:14" x14ac:dyDescent="0.25">
       <c r="D13" s="68" t="s">
         <v>17</v>
       </c>
@@ -2511,7 +2515,7 @@
       </c>
       <c r="N13" s="42"/>
     </row>
-    <row r="14" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:14" x14ac:dyDescent="0.25">
       <c r="D14" s="70" t="s">
         <v>18</v>
       </c>

--- a/material/Week5-Tradeoffs/Week5-Skillcheck.xlsx
+++ b/material/Week5-Tradeoffs/Week5-Skillcheck.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mailmissouri-my.sharepoint.com/personal/btdhd_umsystem_edu/Documents/Desktop/NATR_8001_DecisionAnalysis_Fall25_Mizzou/material/Week5-Tradeoffs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="8_{E84E3B57-7A07-4D7D-A693-35ADA1845EE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{288547FB-48F0-4BCD-BD23-7B316A3C41C0}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="8_{E84E3B57-7A07-4D7D-A693-35ADA1845EE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{41B6C117-596C-459A-9D16-11C116A959A6}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{8E6094A0-F1BF-4785-B38D-3B1B58DBD82F}"/>
+    <workbookView xWindow="9510" yWindow="-90" windowWidth="19380" windowHeight="10260" activeTab="1" xr2:uid="{8E6094A0-F1BF-4785-B38D-3B1B58DBD82F}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="45">
   <si>
     <t>Swing Weighting (example)</t>
   </si>
@@ -307,6 +307,9 @@
   </si>
   <si>
     <t>Citation: Sarah Converse, Mike Runge, Brielle Thompson</t>
+  </si>
+  <si>
+    <t>Neighbor Satisfaction        (Estimated number)</t>
   </si>
 </sst>
 </file>
@@ -1849,7 +1852,7 @@
         <v>10</v>
       </c>
       <c r="C6" s="28" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D6" s="37">
         <v>4</v>
@@ -2072,7 +2075,7 @@
     </row>
     <row r="17" spans="2:8" ht="30" x14ac:dyDescent="0.25">
       <c r="B17" s="27" t="s">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="C17" s="28" t="s">
         <v>11</v>
@@ -2361,19 +2364,19 @@
     </row>
     <row r="7" spans="2:14" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="2" t="s">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D7" s="8">
+        <v>0</v>
+      </c>
+      <c r="E7" s="9">
         <v>5</v>
       </c>
-      <c r="E7" s="9">
+      <c r="F7" s="10">
         <v>0</v>
-      </c>
-      <c r="F7" s="10">
-        <v>5</v>
       </c>
       <c r="G7" s="11"/>
       <c r="H7" s="12"/>
